--- a/Input/urbs_intertemporal_2050/2030.xlsx
+++ b/Input/urbs_intertemporal_2050/2030.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F178A72-5E71-4635-BC6D-0DE13DB1CB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5B81B4-9685-4EC2-B2EA-FCCEB0CA966F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" tabRatio="796" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" tabRatio="796" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -181,9 +181,6 @@
     <t>Coal Plant</t>
   </si>
   <si>
-    <t>Coal Lignite</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT)</t>
   </si>
   <si>
@@ -319,36 +316,44 @@
     <t>EU27.Gas plant</t>
   </si>
   <si>
-    <t>Coal CCUS</t>
-  </si>
-  <si>
-    <t>Coal Lignite CCUS</t>
-  </si>
-  <si>
     <t>Gas Plant (CCGT) CCUS</t>
   </si>
   <si>
-    <t>Piped Gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LNG </t>
-  </si>
-  <si>
-    <t>Gas Plant (CCGT) LNG</t>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Slack</t>
+  </si>
+  <si>
+    <t>Lignite Plant</t>
+  </si>
+  <si>
+    <t>Other non-res</t>
+  </si>
+  <si>
+    <t>Oil Plant</t>
+  </si>
+  <si>
+    <t>Coal Plant CCUS</t>
+  </si>
+  <si>
+    <t>Lignite Plant CCUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -547,7 +552,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -745,12 +750,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1266,7 +1265,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="168" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1397,26 +1396,22 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="363">
     <cellStyle name="20% - Akzent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1783,7 +1778,7 @@
     <cellStyle name="Zelle überprüfen 4" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
     <cellStyle name="Zelle überprüfen 5" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="52">
     <dxf>
       <border>
         <top style="thin">
@@ -1909,6 +1904,340 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -2258,7 +2587,7 @@
       <c r="A3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="62">
+      <c r="B3" s="60">
         <v>316600000</v>
       </c>
       <c r="C3" s="29" t="s">
@@ -2266,7 +2595,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="B4" s="64"/>
+      <c r="B4" s="62"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2291,10 +2620,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="15" customFormat="1">
       <c r="A1" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2309,7 +2638,7 @@
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="63">
+      <c r="B3" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2317,7 +2646,7 @@
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="63">
+      <c r="B4" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2325,7 +2654,7 @@
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="63">
+      <c r="B5" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2333,7 +2662,7 @@
       <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="63">
+      <c r="B6" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2341,7 +2670,7 @@
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="63">
+      <c r="B7" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2349,7 +2678,7 @@
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="63">
+      <c r="B8" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2357,7 +2686,7 @@
       <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="63">
+      <c r="B9" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2365,7 +2694,7 @@
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="63">
+      <c r="B10" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2373,7 +2702,7 @@
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="63">
+      <c r="B11" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2381,7 +2710,7 @@
       <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="63">
+      <c r="B12" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2389,7 +2718,7 @@
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="63">
+      <c r="B13" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2397,7 +2726,7 @@
       <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="63">
+      <c r="B14" s="61">
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -2421,13 +2750,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="15" customFormat="1">
       <c r="A1" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>85</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2446,13 +2775,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2504,7 +2833,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -2607,7 +2936,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>21</v>
@@ -2707,13 +3036,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D10">
-        <v>29.94</v>
+        <v>32.04</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>22</v>
@@ -2722,11 +3051,34 @@
         <v>22</v>
       </c>
     </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>32.04</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:B10">
-    <cfRule type="expression" dxfId="14" priority="1">
+  <conditionalFormatting sqref="B8:B11">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B11">
+    <cfRule type="duplicateValues" dxfId="50" priority="54"/>
   </conditionalFormatting>
   <dataValidations xWindow="307" yWindow="342" count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum commodity use per hour" prompt="For stock commodities, this value limits the energy use per hour (MW)._x000a_" sqref="F1" xr:uid="{1A48ECEE-BF55-4412-BEB7-9CE087C63EE2}"/>
@@ -2743,7 +3095,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -2808,38 +3160,38 @@
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="49" t="s">
-        <v>40</v>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C2" s="20">
         <v>0</v>
       </c>
-      <c r="D2" s="54">
-        <v>46710</v>
+      <c r="D2" s="20">
+        <v>56122</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F2" s="51">
-        <v>0</v>
-      </c>
-      <c r="G2" s="52">
-        <v>2676029.7599999998</v>
-      </c>
-      <c r="H2" s="52">
-        <v>9143.1016799999998</v>
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="54">
+        <v>1784013.3448000001</v>
+      </c>
+      <c r="H2" s="55">
+        <v>28544.213516799999</v>
       </c>
       <c r="I2" s="52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J2" s="53">
         <v>0</v>
       </c>
-      <c r="K2" s="59">
+      <c r="K2" s="57">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L2" s="53">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M2" s="28" t="e">
         <v>#N/A</v>
@@ -2849,38 +3201,38 @@
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="49" t="s">
-        <v>41</v>
+      <c r="B3" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="C3" s="20">
         <v>0</v>
       </c>
-      <c r="D3" s="54">
-        <v>59840</v>
+      <c r="D3" s="20">
+        <v>43599</v>
       </c>
       <c r="E3" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="51">
-        <v>0</v>
-      </c>
-      <c r="G3" s="53">
-        <v>3345037.2</v>
-      </c>
-      <c r="H3" s="53">
-        <v>28432.799999999999</v>
+        <v>0.65</v>
+      </c>
+      <c r="G3" s="52">
+        <v>2230016.6809999999</v>
+      </c>
+      <c r="H3" s="52">
+        <v>47276.353627999997</v>
       </c>
       <c r="I3" s="53">
-        <v>0.35699999999999998</v>
+        <v>4.5</v>
       </c>
       <c r="J3" s="53">
         <v>0</v>
       </c>
-      <c r="K3" s="59">
+      <c r="K3" s="57">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L3" s="53">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M3" s="28" t="e">
         <v>#N/A</v>
@@ -2890,38 +3242,38 @@
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="49" t="s">
-        <v>42</v>
+      <c r="B4" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="20">
         <v>999999</v>
       </c>
       <c r="E4" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="51">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="56">
-        <v>1784013.3448000001</v>
-      </c>
-      <c r="H4" s="57">
-        <v>28544.213516799999</v>
-      </c>
-      <c r="I4" s="52">
-        <v>2.7</v>
-      </c>
-      <c r="J4" s="53">
-        <v>0</v>
-      </c>
-      <c r="K4" s="59">
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="52">
+        <v>769358.55599999998</v>
+      </c>
+      <c r="H4" s="52">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I4" s="53">
+        <v>2.6</v>
+      </c>
+      <c r="J4" s="54">
+        <v>0</v>
+      </c>
+      <c r="K4" s="57">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L4" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M4" s="28" t="e">
         <v>#N/A</v>
@@ -2931,38 +3283,38 @@
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="49" t="s">
-        <v>43</v>
+      <c r="B5" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C5" s="20">
         <v>0</v>
       </c>
-      <c r="D5" s="65">
-        <v>999999</v>
+      <c r="D5" s="20">
+        <v>13483</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="51">
-        <v>0.65</v>
-      </c>
-      <c r="G5" s="52">
-        <v>2230016.6809999999</v>
-      </c>
-      <c r="H5" s="52">
-        <v>47276.353627999997</v>
-      </c>
-      <c r="I5" s="53">
-        <v>4.5</v>
-      </c>
-      <c r="J5" s="53">
-        <v>0</v>
-      </c>
-      <c r="K5" s="59">
-        <v>7.2999999999999995E-2</v>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>5648000</v>
+      </c>
+      <c r="H5" s="63">
+        <v>16725.186000000002</v>
+      </c>
+      <c r="I5">
+        <v>2.6</v>
+      </c>
+      <c r="J5" s="54">
+        <v>0</v>
+      </c>
+      <c r="K5" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L5" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M5" s="28" t="e">
         <v>#N/A</v>
@@ -2972,35 +3324,35 @@
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>44</v>
+      <c r="B6" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C6" s="20">
         <v>0</v>
       </c>
-      <c r="D6" s="65">
-        <v>999999</v>
+      <c r="D6" s="20">
+        <v>14578</v>
       </c>
       <c r="E6" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="52">
-        <v>769358.55599999998</v>
-      </c>
-      <c r="H6" s="52">
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>5648000</v>
+      </c>
+      <c r="H6" s="63">
         <v>16725.186000000002</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6">
         <v>2.6</v>
       </c>
-      <c r="J6" s="56">
-        <v>0</v>
-      </c>
-      <c r="K6" s="59">
-        <v>7.2999999999999995E-2</v>
+      <c r="J6" s="54">
+        <v>0</v>
+      </c>
+      <c r="K6" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L6" s="53">
         <v>25</v>
@@ -3013,38 +3365,38 @@
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="49" t="s">
-        <v>45</v>
+      <c r="B7" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="C7" s="20">
         <v>0</v>
       </c>
-      <c r="D7" s="55">
-        <v>94200</v>
+      <c r="D7" s="20">
+        <v>100000</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="51">
-        <v>0</v>
-      </c>
-      <c r="G7" s="52">
-        <v>5630812.6200000001</v>
-      </c>
-      <c r="H7" s="57">
-        <v>128226.42600000001</v>
-      </c>
-      <c r="I7" s="52">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="J7" s="53">
-        <v>0</v>
-      </c>
-      <c r="K7" s="59">
-        <v>7.2999999999999995E-2</v>
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="53">
+        <v>3512276.2719999999</v>
+      </c>
+      <c r="H7" s="53">
+        <v>72141.039619999996</v>
+      </c>
+      <c r="I7" s="53">
+        <v>6.5</v>
+      </c>
+      <c r="J7" s="54">
+        <v>0</v>
+      </c>
+      <c r="K7" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L7" s="53">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M7" s="28" t="e">
         <v>#N/A</v>
@@ -3054,38 +3406,38 @@
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>46</v>
+      <c r="B8" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C8" s="20">
         <v>0</v>
       </c>
       <c r="D8" s="20">
-        <v>999999999999</v>
+        <v>100000</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="51">
-        <v>0</v>
-      </c>
-      <c r="G8" s="58">
-        <v>5648000</v>
-      </c>
-      <c r="H8" s="58">
-        <v>0</v>
-      </c>
-      <c r="I8" s="58">
-        <v>53.2</v>
-      </c>
-      <c r="J8" s="53">
-        <v>0</v>
-      </c>
-      <c r="K8" s="59">
-        <v>7.2999999999999995E-2</v>
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="53">
+        <v>3813328.52428</v>
+      </c>
+      <c r="H8" s="53">
+        <v>72475.542125599997</v>
+      </c>
+      <c r="I8" s="53">
+        <v>6.7</v>
+      </c>
+      <c r="J8" s="54">
+        <v>0</v>
+      </c>
+      <c r="K8" s="43">
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="L8" s="53">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M8" s="28" t="e">
         <v>#N/A</v>
@@ -3095,38 +3447,38 @@
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="49" t="s">
-        <v>89</v>
+      <c r="B9" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C9" s="20">
         <v>0</v>
       </c>
-      <c r="D9" s="55">
-        <v>0</v>
+      <c r="D9" s="20">
+        <v>100000</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="51">
-        <v>0.5</v>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="53">
-        <v>3512276.2719999999</v>
+        <v>1811895.1500000001</v>
       </c>
       <c r="H9" s="53">
-        <v>72141.039619999996</v>
+        <v>42593.5</v>
       </c>
       <c r="I9" s="53">
-        <v>6.5</v>
-      </c>
-      <c r="J9" s="56">
+        <v>3.33</v>
+      </c>
+      <c r="J9" s="54">
         <v>0</v>
       </c>
       <c r="K9" s="43">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="L9" s="53">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M9" s="28" t="e">
         <v>#N/A</v>
@@ -3137,37 +3489,37 @@
         <v>9</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="C10" s="20">
         <v>0</v>
       </c>
-      <c r="D10" s="55">
-        <v>0</v>
+      <c r="D10" s="20">
+        <v>94198</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="51">
-        <v>0.65</v>
-      </c>
-      <c r="G10" s="53">
-        <v>3813328.52428</v>
-      </c>
-      <c r="H10" s="53">
-        <v>72475.542125599997</v>
-      </c>
-      <c r="I10" s="53">
-        <v>6.7</v>
-      </c>
-      <c r="J10" s="56">
-        <v>0</v>
-      </c>
-      <c r="K10" s="43">
-        <v>7.0999999999999994E-2</v>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="52">
+        <v>5630812.6200000001</v>
+      </c>
+      <c r="H10" s="55">
+        <v>128226.42600000001</v>
+      </c>
+      <c r="I10" s="52">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="J10" s="53">
+        <v>0</v>
+      </c>
+      <c r="K10" s="57">
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="L10" s="53">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M10" s="28" t="e">
         <v>#N/A</v>
@@ -3178,37 +3530,37 @@
         <v>9</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="C11" s="20">
         <v>0</v>
       </c>
-      <c r="D11" s="55">
-        <v>0</v>
+      <c r="D11" s="20">
+        <v>46703</v>
       </c>
       <c r="E11" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G11" s="53">
-        <v>1811895.1500000001</v>
-      </c>
-      <c r="H11" s="53">
-        <v>42593.5</v>
-      </c>
-      <c r="I11" s="53">
-        <v>3.33</v>
-      </c>
-      <c r="J11" s="56">
-        <v>0</v>
-      </c>
-      <c r="K11" s="43">
-        <v>7.0999999999999994E-2</v>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="52">
+        <v>2676029.7599999998</v>
+      </c>
+      <c r="H11" s="52">
+        <v>9143.1016799999998</v>
+      </c>
+      <c r="I11" s="52">
+        <v>0</v>
+      </c>
+      <c r="J11" s="53">
+        <v>0</v>
+      </c>
+      <c r="K11" s="57">
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="L11" s="53">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="M11" s="28" t="e">
         <v>#N/A</v>
@@ -3218,77 +3570,168 @@
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="60" t="s">
-        <v>94</v>
+      <c r="B12" s="49" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="20">
         <v>0</v>
       </c>
-      <c r="D12" s="65">
-        <v>999999</v>
+      <c r="D12" s="20">
+        <v>61218</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="52">
-        <v>769358.55599999998</v>
-      </c>
-      <c r="H12" s="52">
-        <v>16725.186000000002</v>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="53">
+        <v>3345037.2</v>
+      </c>
+      <c r="H12" s="53">
+        <v>28432.799999999999</v>
       </c>
       <c r="I12" s="53">
-        <v>2.6</v>
-      </c>
-      <c r="J12" s="56">
-        <v>0</v>
-      </c>
-      <c r="K12" s="59">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="J12" s="53">
+        <v>0</v>
+      </c>
+      <c r="K12" s="57">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="L12" s="53">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M12" s="28" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0</v>
+      </c>
+      <c r="D13" s="20">
+        <v>999999</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="56">
+        <v>5648000</v>
+      </c>
+      <c r="H13" s="56">
+        <v>0</v>
+      </c>
+      <c r="I13" s="56">
+        <v>53.2</v>
+      </c>
+      <c r="J13" s="53">
+        <v>0</v>
+      </c>
+      <c r="K13" s="43">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="L13" s="53">
+        <v>25</v>
+      </c>
+      <c r="M13" s="28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="A2:A12 B2:B3 C2:C12 M2:M4 P2:XFD4">
-    <cfRule type="expression" dxfId="13" priority="3">
+  <conditionalFormatting sqref="P2:XFD4">
+    <cfRule type="expression" dxfId="49" priority="35">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:F3 A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="12" priority="17">
+  <conditionalFormatting sqref="A1:XFD1 A14:F14 L14:XFD14 A15:XFD1048576 N13:XFD13">
+    <cfRule type="expression" dxfId="48" priority="53">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1 A13:F14 L13:XFD14 A15:XFD1048576">
-    <cfRule type="expression" dxfId="11" priority="21">
+  <conditionalFormatting sqref="N12:XFD12">
+    <cfRule type="expression" dxfId="47" priority="36">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B12">
-    <cfRule type="expression" dxfId="10" priority="1">
+  <conditionalFormatting sqref="C2:D13 F9:F13 F4:F6">
+    <cfRule type="expression" dxfId="46" priority="14">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="9" priority="12">
+  <conditionalFormatting sqref="E2:E4 E12:E13">
+    <cfRule type="expression" dxfId="45" priority="13">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:I2">
-    <cfRule type="expression" dxfId="8" priority="11">
+  <conditionalFormatting sqref="F2">
+    <cfRule type="expression" dxfId="44" priority="12">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N12:XFD12">
-    <cfRule type="expression" dxfId="7" priority="4">
+  <conditionalFormatting sqref="F7">
+    <cfRule type="expression" dxfId="43" priority="11">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B9">
+    <cfRule type="expression" dxfId="42" priority="10">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="41" priority="9">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="expression" dxfId="40" priority="8">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" dxfId="39" priority="7">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="38" priority="6">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="expression" dxfId="37" priority="5">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" dxfId="36" priority="4">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2">
+    <cfRule type="expression" dxfId="35" priority="3">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M11:M12">
+    <cfRule type="expression" dxfId="34" priority="1">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:I11">
+    <cfRule type="expression" dxfId="33" priority="2">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3315,7 +3758,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -3335,24 +3778,24 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="60" t="s">
-        <v>43</v>
+      <c r="A2" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="24">
         <v>1</v>
@@ -3362,16 +3805,16 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="60" t="s">
-        <v>43</v>
+      <c r="A3" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="61">
+        <v>50</v>
+      </c>
+      <c r="D3" s="59">
         <v>0.42</v>
       </c>
       <c r="E3" s="24" t="e">
@@ -3380,14 +3823,14 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="60" t="s">
-        <v>43</v>
+      <c r="A4" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="24">
         <v>0.36299999999999999</v>
@@ -3397,14 +3840,14 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="60" t="s">
-        <v>44</v>
+      <c r="A5" s="58" t="s">
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="24">
         <v>1</v>
@@ -3414,16 +3857,16 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="60" t="s">
-        <v>44</v>
+      <c r="A6" s="58" t="s">
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="61">
+        <v>50</v>
+      </c>
+      <c r="D6" s="59">
         <v>0.61</v>
       </c>
       <c r="E6" s="24" t="e">
@@ -3432,14 +3875,14 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="60" t="s">
-        <v>44</v>
+      <c r="A7" s="58" t="s">
+        <v>43</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="48">
         <v>0.1855</v>
@@ -3450,14 +3893,14 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="60" t="s">
-        <v>46</v>
+      <c r="A8" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -3468,14 +3911,14 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="60" t="s">
-        <v>46</v>
+      <c r="A9" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="24">
         <v>0.35</v>
@@ -3486,14 +3929,14 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="60" t="s">
-        <v>46</v>
+      <c r="A10" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="24">
         <v>0</v>
@@ -3504,14 +3947,14 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="60" t="s">
-        <v>45</v>
+      <c r="A11" s="58" t="s">
+        <v>44</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="24">
         <v>1</v>
@@ -3522,14 +3965,14 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="60" t="s">
-        <v>45</v>
+      <c r="A12" s="58" t="s">
+        <v>44</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="24">
         <v>0.38</v>
@@ -3540,14 +3983,14 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="58" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="24">
         <v>1</v>
@@ -3557,16 +4000,16 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="58" t="s">
         <v>42</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="61">
+        <v>50</v>
+      </c>
+      <c r="D14" s="59">
         <v>0.46</v>
       </c>
       <c r="E14" s="24" t="e">
@@ -3575,14 +4018,14 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="58" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="24">
         <v>0.34179999999999999</v>
@@ -3593,14 +4036,14 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="58" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="24">
         <v>1</v>
@@ -3611,14 +4054,14 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="58" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="24">
         <v>1</v>
@@ -3629,14 +4072,14 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="60" t="s">
+      <c r="A18" s="58" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="24">
         <v>1</v>
@@ -3647,14 +4090,14 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="58" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="24">
         <v>1</v>
@@ -3665,14 +4108,14 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="60" t="s">
-        <v>89</v>
+      <c r="A20" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="24">
         <v>1</v>
@@ -3683,14 +4126,14 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="60" t="s">
-        <v>89</v>
+      <c r="A21" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="24">
         <v>3.6999999999999998E-2</v>
@@ -3701,14 +4144,14 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="60" t="s">
-        <v>89</v>
+      <c r="A22" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D22" s="24">
         <v>3.4180000000000002E-2</v>
@@ -3719,14 +4162,14 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="60" t="s">
-        <v>90</v>
+      <c r="A23" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" s="24">
         <v>1</v>
@@ -3737,14 +4180,14 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="60" t="s">
-        <v>90</v>
+      <c r="A24" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="24">
         <v>0.33</v>
@@ -3755,14 +4198,14 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="60" t="s">
-        <v>90</v>
+      <c r="A25" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25" s="24">
         <v>3.6299999999999999E-2</v>
@@ -3773,14 +4216,14 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="60" t="s">
-        <v>91</v>
+      <c r="A26" s="58" t="s">
+        <v>88</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="24">
         <v>1</v>
@@ -3790,14 +4233,14 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="60" t="s">
-        <v>91</v>
+      <c r="A27" s="58" t="s">
+        <v>88</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D27" s="24">
         <v>0.46</v>
@@ -3808,14 +4251,14 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="60" t="s">
-        <v>91</v>
+      <c r="A28" s="58" t="s">
+        <v>88</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" s="24">
         <v>1.8550000000000001E-2</v>
@@ -3826,34 +4269,35 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="60" t="s">
-        <v>94</v>
+      <c r="A29" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="24">
         <v>1</v>
       </c>
-      <c r="E29" s="24">
-        <v>1.2</v>
+      <c r="E29" s="24" t="e">
+        <f>D29*E27</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="60" t="s">
-        <v>94</v>
+      <c r="A30" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="61">
-        <v>0.61</v>
+        <v>50</v>
+      </c>
+      <c r="D30" s="24">
+        <v>0.4</v>
       </c>
       <c r="E30" s="24" t="e">
         <f>NA()</f>
@@ -3861,49 +4305,95 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="60" t="s">
-        <v>94</v>
+      <c r="A31" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="48">
-        <v>0.1855</v>
-      </c>
-      <c r="E31" s="24">
-        <f>D31*E29</f>
-        <v>0.22259999999999999</v>
+        <v>50</v>
+      </c>
+      <c r="D31" s="24">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E31" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="24">
+        <v>1</v>
+      </c>
+      <c r="E32" s="24" t="e">
+        <f>D32*E30</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="24">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="E34" s="24" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A30:C31 E30:E31 A2:C4 E2:XFD19">
-    <cfRule type="expression" dxfId="6" priority="6">
+  <conditionalFormatting sqref="F2:XFD19">
+    <cfRule type="expression" dxfId="32" priority="65">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29:E29">
-    <cfRule type="expression" dxfId="5" priority="1">
+  <conditionalFormatting sqref="A1:XFD1">
+    <cfRule type="expression" dxfId="30" priority="83">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1 A5 C5 A6:C19">
-    <cfRule type="expression" dxfId="4" priority="24">
+  <conditionalFormatting sqref="A20:XFD25 F26:XFD26 A27:XFD28 F29:XFD31 A32:XFD32 A66:XFD1048576 F33:XFD65">
+    <cfRule type="expression" dxfId="29" priority="66">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:XFD25 A26 C26:XFD26 A27:XFD28 F29:XFD31 A32:XFD1048576">
-    <cfRule type="expression" dxfId="3" priority="7">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D5 D8:D13 D15:D19 D2">
-    <cfRule type="expression" dxfId="2" priority="14">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-    <cfRule type="dataBar" priority="23">
+  <conditionalFormatting sqref="D1:E1">
+    <cfRule type="dataBar" priority="105">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3911,8 +4401,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D10 D5 D2 E2:E7">
-    <cfRule type="dataBar" priority="21">
+  <conditionalFormatting sqref="D66:E1048576">
+    <cfRule type="dataBar" priority="112">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3920,53 +4410,28 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="dataBar" priority="17">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13 D15">
-    <cfRule type="dataBar" priority="15">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="dataBar" priority="13">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D17">
-    <cfRule type="dataBar" priority="20">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D19">
-    <cfRule type="dataBar" priority="19">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D29">
-    <cfRule type="dataBar" priority="5">
+  <conditionalFormatting sqref="A5 A6:C19 D8:E12 B2:C4 D16:E19">
+    <cfRule type="expression" dxfId="27" priority="53">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:C25 C26 B27:C27">
+    <cfRule type="expression" dxfId="26" priority="44">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:C20 A26:A28">
+    <cfRule type="expression" dxfId="25" priority="45">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" dxfId="24" priority="38">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="dataBar" priority="58">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -3974,38 +4439,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D3754D5A-8BC7-45DB-B032-709D34580FDC}</x14:id>
+          <x14:id>{1FB5413F-C60C-481C-BC4D-5EA669622A1D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:E1">
-    <cfRule type="dataBar" priority="46">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:E28">
-    <cfRule type="dataBar" priority="8">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="9">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D29:E29 E30:E31">
-    <cfRule type="dataBar" priority="4">
+  <conditionalFormatting sqref="D8:D12 D16:D19">
+    <cfRule type="dataBar" priority="52">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4013,58 +4453,364 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2EC056F3-C092-4AA1-91DB-7DEBA3251A54}</x14:id>
+          <x14:id>{C217AE55-0B56-4455-982E-C7007C36640D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D32:E1048576">
-    <cfRule type="dataBar" priority="53">
+  <conditionalFormatting sqref="D11:E12">
+    <cfRule type="dataBar" priority="59">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E10">
-    <cfRule type="dataBar" priority="29">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C90A5EBB-3B5C-4A1D-BC37-6EE22A22E610}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:E17">
+    <cfRule type="dataBar" priority="55">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E12">
-    <cfRule type="dataBar" priority="32">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{98D21345-FF12-4B10-98AC-BCD316B413E1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:E19">
+    <cfRule type="dataBar" priority="54">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E15">
-    <cfRule type="dataBar" priority="27">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7476DF7F-053F-4D2B-ADAD-1FA9F631CF7A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E10">
+    <cfRule type="dataBar" priority="57">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16:E17">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B5E62FF1-655B-4398-8B75-6D6284217A76}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:E34">
+    <cfRule type="expression" dxfId="22" priority="37">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:C28">
+    <cfRule type="expression" dxfId="21" priority="40">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="expression" dxfId="20" priority="36">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:A31">
+    <cfRule type="expression" dxfId="19" priority="35">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:A34">
+    <cfRule type="expression" dxfId="18" priority="34">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29 B30:C30">
+    <cfRule type="expression" dxfId="17" priority="32">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="dataBar" priority="31">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{64F3DBB3-11DC-4D2C-B90A-48D0B36AFD38}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30">
+    <cfRule type="dataBar" priority="33">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6551159E-E598-4B0E-B273-9E04984A3E74}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31">
+    <cfRule type="dataBar" priority="30">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5F33B821-F9A4-40E6-B9A3-002229BB64A5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:C31">
+    <cfRule type="expression" dxfId="16" priority="29">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32 B33:C33">
+    <cfRule type="expression" dxfId="15" priority="27">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32">
     <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
         <color rgb="FF638EC6"/>
       </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E19">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C96E66FB-A298-49D3-98DC-059B1D484C6F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E33">
+    <cfRule type="dataBar" priority="28">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{918173F3-E2B6-456B-99B3-3A372666A5A5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E34">
     <cfRule type="dataBar" priority="25">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7D2B150B-284F-4022-9BF4-D37C0CD6DB01}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:C34">
+    <cfRule type="expression" dxfId="14" priority="24">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A22">
+    <cfRule type="expression" dxfId="13" priority="23">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:A25">
+    <cfRule type="expression" dxfId="12" priority="22">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="expression" dxfId="11" priority="20">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D8A17A91-9240-4F68-9B8C-5A45D62207B3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:D34">
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{31502459-506E-4430-A0C0-84A3CB03AA20}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4">
+    <cfRule type="expression" dxfId="8" priority="14">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2 D4">
+    <cfRule type="expression" dxfId="7" priority="15">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2 D4">
+    <cfRule type="dataBar" priority="18">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4 D2">
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E7">
+    <cfRule type="expression" dxfId="6" priority="10">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" dxfId="5" priority="11">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E7 D5">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13 D15">
+    <cfRule type="expression" dxfId="3" priority="6">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15 D13">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15 D13">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E15">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E28">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E28">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="2"/>
@@ -4082,7 +4828,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3754D5A-8BC7-45DB-B032-709D34580FDC}">
+          <x14:cfRule type="dataBar" id="{1FB5413F-C60C-481C-BC4D-5EA669622A1D}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4094,10 +4840,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D29</xm:sqref>
+          <xm:sqref>D8:D10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2EC056F3-C092-4AA1-91DB-7DEBA3251A54}">
+          <x14:cfRule type="dataBar" id="{C217AE55-0B56-4455-982E-C7007C36640D}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4109,7 +4855,187 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D29:E29 E30:E31</xm:sqref>
+          <xm:sqref>D8:D12 D16:D19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C90A5EBB-3B5C-4A1D-BC37-6EE22A22E610}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D11:E12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{98D21345-FF12-4B10-98AC-BCD316B413E1}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D16:E17</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7476DF7F-053F-4D2B-ADAD-1FA9F631CF7A}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D18:E19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B5E62FF1-655B-4398-8B75-6D6284217A76}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E8:E10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{64F3DBB3-11DC-4D2C-B90A-48D0B36AFD38}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6551159E-E598-4B0E-B273-9E04984A3E74}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E30</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5F33B821-F9A4-40E6-B9A3-002229BB64A5}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E31</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C96E66FB-A298-49D3-98DC-059B1D484C6F}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{918173F3-E2B6-456B-99B3-3A372666A5A5}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E33</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7D2B150B-284F-4022-9BF4-D37C0CD6DB01}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D8A17A91-9240-4F68-9B8C-5A45D62207B3}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:D34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{31502459-506E-4430-A0C0-84A3CB03AA20}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:D34</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4141,19 +5067,19 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>53</v>
-      </c>
-      <c r="C1" t="s">
-        <v>54</v>
       </c>
       <c r="D1" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>33</v>
@@ -4177,13 +5103,13 @@
         <v>38</v>
       </c>
       <c r="M1" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4245,46 +5171,46 @@
         <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="M1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>70</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>71</v>
       </c>
       <c r="P1" s="16" t="s">
         <v>37</v>
@@ -4293,13 +5219,13 @@
         <v>38</v>
       </c>
       <c r="R1" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="T1" s="36" t="s">
         <v>73</v>
-      </c>
-      <c r="T1" s="36" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -4307,7 +5233,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="39" t="s">
         <v>18</v>
@@ -4367,7 +5293,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>18</v>
@@ -4428,7 +5354,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>18</v>
@@ -4541,19 +5467,19 @@
         <v>11</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -4596,10 +5522,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
